--- a/output/graficos_nacionales/plot_nacional_e_supneta_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_supneta_a_2020.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -8972,7 +8972,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -10398,7 +10398,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -10490,7 +10490,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -14354,7 +14354,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -14998,7 +14998,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -15366,7 +15366,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -15412,7 +15412,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_e_supneta_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_supneta_a_2020.xlsx
@@ -2083,7 +2083,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:46</t>
+    <t xml:space="preserve">2026-09-07 12:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_supneta_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_supneta_a_2020.xlsx
@@ -2083,7 +2083,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:52</t>
+    <t xml:space="preserve">2026-09-08 10:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
